--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maman laisse Baptiste dans la cour. Les chaussures tapent le sol. Noa arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Baptiste le regarde. Maman est encore près du portail. Elle dit : beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Baptiste hoche la tête. Ils font une file pour le cerceau. Noa a envie d'aller vite. Baptiste dit : on peut attendre. Noa souffle. Il reste dans la file. Ils jouent. Plus tard, au jardin de l'école, Noa a encore de l'énergie. Ce n'est pas une faute. Baptiste va vers la maîtresse. Il demande à un adulte. La maîtresse marche avec Noa jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Maman revient. Baptiste dit : Noa a de l'énergie. Maman dit : ce n'est pas une faute.</t>
+          <t>Maman laisse Baptiste dans la cour. Les chaussures tapent le sol. Noa arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Baptiste le regarde. Maman est encore près du portail. Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Baptiste hoche la tête. Ils font une file pour le cerceau. Noa a envie d'aller vite. On peut attendre. Noa souffle. Il reste dans la file. Ils jouent. Plus tard, au jardin de l'école, Noa a encore de l'énergie. Ce n'est pas une faute. Baptiste va vers la maîtresse. Il demande à un adulte. La maîtresse marche avec Noa jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Maman revient. Noa a de l'énergie. Ce n'est pas une faute.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Maman laisse Baptiste dans la cour. Les chaussures tapent le sol. Noa arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Baptiste le regarde. Maman est encore près du portail.
+narrateur|Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte.
+narrateur|Baptiste hoche la tête. Ils font une file pour le cerceau. Noa a envie d'aller vite.
+enfant-m|On peut attendre.
+narrateur|Noa souffle. Il reste dans la file. Ils jouent. Plus tard, au jardin de l'école, Noa a encore de l'énergie. Ce n'est pas une faute. Baptiste va vers la maîtresse. Il demande à un adulte. La maîtresse marche avec Noa jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Maman revient.
+enfant-m|Noa a de l'énergie.
+maman|Ce n'est pas une faute.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noa a de l'énergie. Que peut-on faire ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1669,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noa a de l'énergie. Ce n'est pas une faute. Baptiste a joué. Il a su attendre. Il a demandé à un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1836,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Maman prend la main de Baptiste. Noa range un cerceau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2003,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2043,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 maman|Ce n'est pas une faute.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Noa a de l'énergie. Que peut-on faire ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1674,6 +1681,7 @@
           <t>narrateur|Noa a de l'énergie. Ce n'est pas une faute. Baptiste a joué. Il a su attendre. Il a demandé à un adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1841,6 +1849,7 @@
           <t>narrateur|Maman prend la main de Baptiste. Noa range un cerceau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2008,6 +2017,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2026,7 +2036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2050,6 +2060,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2251,6 +2275,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Baptiste joue avec l'énergie de Noa</t>
+          <t>La file du cerceau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut le cerceau sous l'arbre. Chouchou a de l'énergie. Ils font une file. Amir demande à papa. Ils versent l'eau au bac.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Maman laisse Baptiste dans la cour. Les chaussures tapent le sol. Noa arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Baptiste le regarde. Maman est encore près du portail. Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Baptiste hoche la tête. Ils font une file pour le cerceau. Noa a envie d'aller vite. On peut attendre. Noa souffle. Il reste dans la file. Ils jouent. Plus tard, au jardin de l'école, Noa a encore de l'énergie. Ce n'est pas une faute. Baptiste va vers la maîtresse. Il demande à un adulte. La maîtresse marche avec Noa jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Maman revient. Noa a de l'énergie. Ce n'est pas une faute.</t>
+          <t>L'ombre du grand arbre fait un puzzle par terre. Une cloche lointaine fait ding, tout loin. Un peu de poussière de craie flotte dans l'air. Un cerceau dort dans l'herbe. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir écoute les feuilles. Je veux le cerceau. Il est sous l'arbre. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Il saute tout le temps. Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Amir hoche la tête. Ils font une file pour le cerceau. Chouchou a envie d'aller vite. On peut attendre. Chouchou souffle. Il reste dans la file. Bravo, Chouchou. Tu as attendu. Ils jouent. Le cerceau tourne dans l'ombre. Plus tard, au jardin de l'école, Chouchou a encore de l'énergie. Ce n'est pas une faute. Amir va vers papa. Papa, on fait quoi ? On marche jusqu'au bac. Papa marche avec Chouchou jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Amir attend son tour pour verser. Bravo, Amir. Tu as demandé. C'est du bon travail. Les feuilles bougent un peu. Chouchou a de l'énergie. Ce n'est pas une faute.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,62 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Maman laisse Baptiste dans la cour. Les chaussures tapent le sol. Noa arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Baptiste le regarde. Maman est encore près du portail.
-narrateur|Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte.
-narrateur|Baptiste hoche la tête. Ils font une file pour le cerceau. Noa a envie d'aller vite.
+          <t>narrateur|L'ombre du grand arbre fait un puzzle par terre.
+narrateur|Une cloche lointaine fait ding, tout loin.
+narrateur|Un peu de poussière de craie flotte dans l'air.
+narrateur|Un cerceau dort dans l'herbe.
+narrateur|Papa noue un lacet.
+papa|Ton lacet est prêt, Amir ?
+enfant-m|Oui, papa.
+narrateur|Maman glisse une gourde dans le sac.
+maman|L'eau est fraîche.
+narrateur|En ce moment, Amir écoute les feuilles.
+enfant-m|Je veux le cerceau.
+papa|Il est sous l'arbre.
+narrateur|Les chaussures tapent le sol de la cour.
+narrateur|Chouchou arrive en sautant.
+narrateur|Il a beaucoup d'énergie.
+narrateur|Il tourne.
+narrateur|Il s'arrête.
+narrateur|Il recommence.
+enfant-m|Il saute tout le temps.
+maman|Beaucoup d'énergie, ce n'est pas une faute.
+maman|On peut jouer.
+maman|On peut attendre.
+maman|On peut demander à un adulte.
+narrateur|Amir hoche la tête.
+narrateur|Ils font une file pour le cerceau.
+narrateur|Chouchou a envie d'aller vite.
 enfant-m|On peut attendre.
-narrateur|Noa souffle. Il reste dans la file. Ils jouent. Plus tard, au jardin de l'école, Noa a encore de l'énergie. Ce n'est pas une faute. Baptiste va vers la maîtresse. Il demande à un adulte. La maîtresse marche avec Noa jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Maman revient.
-enfant-m|Noa a de l'énergie.
+narrateur|Chouchou souffle.
+narrateur|Il reste dans la file.
+papa|Bravo, Chouchou.
+papa|Tu as attendu.
+narrateur|Ils jouent.
+narrateur|Le cerceau tourne dans l'ombre.
+narrateur|Plus tard, au jardin de l'école, Chouchou a encore de l'énergie.
+maman|Ce n'est pas une faute.
+narrateur|Amir va vers papa.
+enfant-m|Papa, on fait quoi ?
+papa|On marche jusqu'au bac.
+narrateur|Papa marche avec Chouchou jusqu'au bac.
+narrateur|L'eau est froide.
+narrateur|Puis ils versent l'eau ensemble.
+maman|On peut jouer ou attendre.
+narrateur|Amir attend son tour pour verser.
+papa|Bravo, Amir.
+papa|Tu as demandé.
+papa|C'est du bon travail.
+narrateur|Les feuilles bougent un peu.
+enfant-m|Chouchou a de l'énergie.
 maman|Ce n'est pas une faute.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noa a de l'énergie. Que peut-on faire ?</t>
+          <t>Chouchou a de l'énergie. Que peut-on faire ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1564,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noa a de l'énergie. Que peut-on faire ?</t>
+          <t>narrateur|Chouchou a de l'énergie. Que peut-on faire ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1592,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noa a de l'énergie. Ce n'est pas une faute. Baptiste a joué. Il a su attendre. Il a demandé à un adulte.</t>
+          <t>L'eau du bac brille sous l'arbre. Chouchou a de l'énergie. Ce n'est pas une faute. Amir a joué. Il a su attendre. Il a demandé à un adulte. Tu as demandé, Amir ? Oui, papa. Bravo. Tu as fait du bon travail. Ils versent encore un peu d'eau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1736,17 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noa a de l'énergie. Ce n'est pas une faute. Baptiste a joué. Il a su attendre. Il a demandé à un adulte.</t>
+          <t>narrateur|L'eau du bac brille sous l'arbre.
+narrateur|Chouchou a de l'énergie.
+maman|Ce n'est pas une faute.
+narrateur|Amir a joué.
+narrateur|Il a su attendre.
+narrateur|Il a demandé à un adulte.
+papa|Tu as demandé, Amir ?
+enfant-m|Oui, papa.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Ils versent encore un peu d'eau.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend la main de Baptiste. Noa range un cerceau.</t>
+          <t>On reprend le sac ? Oui, maman. Maman prend la main d'Amir. Chouchou range un cerceau. Vous vous dites au revoir ? Au revoir. Au revoir, Chouchou. Bravo. Belle file, aujourd'hui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1846,7 +1914,14 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman prend la main de Baptiste. Noa range un cerceau.</t>
+          <t>maman|On reprend le sac ?
+enfant-m|Oui, maman.
+narrateur|Maman prend la main d'Amir.
+narrateur|Chouchou range un cerceau.
+papa|Vous vous dites au revoir ?
+copain|Au revoir.
+enfant-m|Au revoir, Chouchou.
+papa|Bravo. Belle file, aujourd'hui.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1874,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>On a fait la file du cerceau. On a attendu. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2014,7 +2089,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|On a fait la file du cerceau.
+enfant-m|On a attendu.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2036,7 +2115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2074,6 +2153,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du grand arbre fait un puzzle par terre. Une cloche lointaine fait ding, tout loin. Un peu de poussière de craie flotte dans l'air. Un cerceau dort dans l'herbe. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir écoute les feuilles. Je veux le cerceau. Il est sous l'arbre. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Il saute tout le temps. Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Amir hoche la tête. Ils font une file pour le cerceau. Chouchou a envie d'aller vite. On peut attendre. Chouchou souffle. Il reste dans la file. Bravo, Chouchou. Tu as attendu. Ils jouent. Le cerceau tourne dans l'ombre. Plus tard, au jardin de l'école, Chouchou a encore de l'énergie. Ce n'est pas une faute. Amir va vers papa. Papa, on fait quoi ? On marche jusqu'au bac. Papa marche avec Chouchou jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Amir attend son tour pour verser. Bravo, Amir. Tu as demandé. C'est du bon travail. Les feuilles bougent un peu. Chouchou a de l'énergie. Ce n'est pas une faute.</t>
+          <t>L'ombre du grand arbre fait un puzzle par terre. Une cloche lointaine fait ding, tout loin. Un peu de poussière de craie flotte dans l'air. Un cerceau dort dans l'herbe. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir écoute les feuilles. Je veux le cerceau. Il est sous l'arbre. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Il saute tout le temps. Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Amir hoche la tête. Ils font une file pour le cerceau. Chouchou a envie d'aller vite. On peut attendre. Chouchou souffle. Il reste dans la file. Bravo, Chouchou. Tu as attendu. Ils jouent. Le cerceau tourne dans l'ombre. Plus tard, au jardin de l'école, Chouchou a encore de l'énergie. Ce n'est pas une faute. Amir va vers papa. Papa, on fait quoi ? On marche jusqu'au bac. Papa marche avec Chouchou jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Amir attend son tour pour verser. Bravo, Amir. Tu as demandé. C'est du bon travail. Les feuilles bougent un peu. Chouchou a de l'énergie. Ce n'est pas une faute. Une feuille tombe dans l'eau. Elle tourne, tout lentement. On la laisse flotter ? Oui. Chouchou regarde la feuille. Il attend. Bravo. Vous jouez tout près.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1372,7 +1372,15 @@
 papa|C'est du bon travail.
 narrateur|Les feuilles bougent un peu.
 enfant-m|Chouchou a de l'énergie.
-maman|Ce n'est pas une faute.</t>
+maman|Ce n'est pas une faute.
+narrateur|Une feuille tombe dans l'eau.
+narrateur|Elle tourne, tout lentement.
+papa|On la laisse flotter ?
+enfant-m|Oui.
+narrateur|Chouchou regarde la feuille.
+narrateur|Il attend.
+maman|Bravo.
+maman|Vous jouez tout près.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1564,7 +1572,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Chouchou a de l'énergie. Que peut-on faire ?</t>
+          <t>narrateur|Chouchou a de l'énergie.
+narrateur|Que peut-on faire ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1921,7 +1930,8 @@
 papa|Vous vous dites au revoir ?
 copain|Au revoir.
 enfant-m|Au revoir, Chouchou.
-papa|Bravo. Belle file, aujourd'hui.</t>
+papa|Bravo.
+papa|Belle file, aujourd'hui.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -2115,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2158,6 +2168,34 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La file du cerceau</t>
+          <t>Le bateau-feuille</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir veut le cerceau sous l'arbre. Chouchou a de l'énergie. Ils font une file. Amir demande à papa. Ils versent l'eau au bac.</t>
+          <t>Amir veut faire flotter une feuille jaune dans le bac. Chouchou arrive avec beaucoup d'énergie. L'eau éclabousse. Ils jouent, ils attendent, Amir demande à papa. La feuille tourne, tout lentement.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>L'ombre du grand arbre fait un puzzle par terre. Une cloche lointaine fait ding, tout loin. Un peu de poussière de craie flotte dans l'air. Un cerceau dort dans l'herbe. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir écoute les feuilles. Je veux le cerceau. Il est sous l'arbre. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Il a beaucoup d'énergie. Il tourne. Il s'arrête. Il recommence. Il saute tout le temps. Beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Amir hoche la tête. Ils font une file pour le cerceau. Chouchou a envie d'aller vite. On peut attendre. Chouchou souffle. Il reste dans la file. Bravo, Chouchou. Tu as attendu. Ils jouent. Le cerceau tourne dans l'ombre. Plus tard, au jardin de l'école, Chouchou a encore de l'énergie. Ce n'est pas une faute. Amir va vers papa. Papa, on fait quoi ? On marche jusqu'au bac. Papa marche avec Chouchou jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Amir attend son tour pour verser. Bravo, Amir. Tu as demandé. C'est du bon travail. Les feuilles bougent un peu. Chouchou a de l'énergie. Ce n'est pas une faute. Une feuille tombe dans l'eau. Elle tourne, tout lentement. On la laisse flotter ? Oui. Chouchou regarde la feuille. Il attend. Bravo. Vous jouez tout près.</t>
+          <t>Une craie blanche a roulé sous le banc. Elle a un ventre cassé. Un morceau reste, tout sec. L'ombre du grand arbre fait des taches par terre. Une cloche lointaine fait ding, tout loin. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir ramasse une feuille jaune. Elle est sèche. Elle a des nervures. Elle craque un tout petit peu. Je veux un bateau. Dans le bac. Le bac est sous l'arbre. Amir souffle sur la feuille. Elle tremble dans sa main. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Elle a beaucoup d'énergie. Elle tourne. Elle s'arrête. Elle recommence. Elle saute tout le temps. C'est son énergie. Ce n'est pas une faute. Ils font une file pour le bac. Chouchou a envie d'aller vite. L'eau éclabousse un peu. Ma feuille. La feuille jaune tremble au bord. Amir regarde papa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman laisse Baptiste dans la cour. Les chaussures tapent le sol. Noa arrive en sautant. Il a beaucoup d'&lt;emphasis level="moderate"&gt;énergie&lt;/emphasis&gt;. Il tourne. Il s'arrête. Il recommence. Baptiste le regarde. Maman est encore près du portail. Elle dit : beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Baptiste hoche la tête. Ils font une file pour le cerceau. Noa a envie d'aller vite. Baptiste dit : on peut attendre. Noa souffle. Il reste dans la file. Ils jouent. Plus tard, au jardin de l'école, Noa a encore de l'énergie. Ce n'est pas une faute. Baptiste va vers la maîtresse. Il demande à un adulte. La maîtresse marche avec Noa jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Maman revient. Baptiste dit : Noa a de l'énergie. Maman dit : ce n'est pas une faute.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une craie blanche a roulé sous le banc. Elle a un ventre cassé. Un morceau reste, tout sec. L'ombre du grand arbre fait des taches par terre. Une cloche lointaine fait ding, tout loin. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir ramasse une feuille jaune. Elle est sèche. Elle a des nervures. Elle craque un tout petit peu. Je veux un bateau. Dans le bac. Le bac est sous l'arbre. Amir souffle sur la feuille. Elle tremble dans sa main. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Elle a beaucoup d'énergie. Elle tourne. Elle s'arrête. Elle recommence. Elle saute tout le temps. C'est son énergie. Ce n'est pas une faute. Ils font une file pour le bac. Chouchou a envie d'aller vite. L'eau éclabousse un peu. Ma feuille. La feuille jaune tremble au bord. Amir regarde papa.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,63 +1324,40 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|L'ombre du grand arbre fait un puzzle par terre.
+          <t>narrateur|Une craie blanche a roulé sous le banc.
+narrateur|Elle a un ventre cassé.
+narrateur|Un morceau reste, tout sec.
+narrateur|L'ombre du grand arbre fait des taches par terre.
 narrateur|Une cloche lointaine fait ding, tout loin.
-narrateur|Un peu de poussière de craie flotte dans l'air.
-narrateur|Un cerceau dort dans l'herbe.
 narrateur|Papa noue un lacet.
 papa|Ton lacet est prêt, Amir ?
 enfant-m|Oui, papa.
 narrateur|Maman glisse une gourde dans le sac.
 maman|L'eau est fraîche.
-narrateur|En ce moment, Amir écoute les feuilles.
-enfant-m|Je veux le cerceau.
-papa|Il est sous l'arbre.
+narrateur|En ce moment, Amir ramasse une feuille jaune.
+narrateur|Elle est sèche.
+narrateur|Elle a des nervures.
+narrateur|Elle craque un tout petit peu.
+enfant-m|Je veux un bateau.
+enfant-m|Dans le bac.
+papa|Le bac est sous l'arbre.
+narrateur|Amir souffle sur la feuille.
+narrateur|Elle tremble dans sa main.
 narrateur|Les chaussures tapent le sol de la cour.
 narrateur|Chouchou arrive en sautant.
-narrateur|Il a beaucoup d'énergie.
-narrateur|Il tourne.
-narrateur|Il s'arrête.
-narrateur|Il recommence.
-enfant-m|Il saute tout le temps.
-maman|Beaucoup d'énergie, ce n'est pas une faute.
-maman|On peut jouer.
-maman|On peut attendre.
-maman|On peut demander à un adulte.
-narrateur|Amir hoche la tête.
-narrateur|Ils font une file pour le cerceau.
+narrateur|Elle a beaucoup d'énergie.
+narrateur|Elle tourne.
+narrateur|Elle s'arrête.
+narrateur|Elle recommence.
+enfant-m|Elle saute tout le temps.
+maman|C'est son énergie.
+maman|Ce n'est pas une faute.
+narrateur|Ils font une file pour le bac.
 narrateur|Chouchou a envie d'aller vite.
-enfant-m|On peut attendre.
-narrateur|Chouchou souffle.
-narrateur|Il reste dans la file.
-papa|Bravo, Chouchou.
-papa|Tu as attendu.
-narrateur|Ils jouent.
-narrateur|Le cerceau tourne dans l'ombre.
-narrateur|Plus tard, au jardin de l'école, Chouchou a encore de l'énergie.
-maman|Ce n'est pas une faute.
-narrateur|Amir va vers papa.
-enfant-m|Papa, on fait quoi ?
-papa|On marche jusqu'au bac.
-narrateur|Papa marche avec Chouchou jusqu'au bac.
-narrateur|L'eau est froide.
-narrateur|Puis ils versent l'eau ensemble.
-maman|On peut jouer ou attendre.
-narrateur|Amir attend son tour pour verser.
-papa|Bravo, Amir.
-papa|Tu as demandé.
-papa|C'est du bon travail.
-narrateur|Les feuilles bougent un peu.
-enfant-m|Chouchou a de l'énergie.
-maman|Ce n'est pas une faute.
-narrateur|Une feuille tombe dans l'eau.
-narrateur|Elle tourne, tout lentement.
-papa|On la laisse flotter ?
-enfant-m|Oui.
-narrateur|Chouchou regarde la feuille.
-narrateur|Il attend.
-maman|Bravo.
-maman|Vous jouez tout près.</t>
+narrateur|L'eau éclabousse un peu.
+enfant-m|Ma feuille.
+narrateur|La feuille jaune tremble au bord.
+narrateur|Amir regarde papa.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1417,7 +1394,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noa a de l'&lt;emphasis level="moderate"&gt;énergie&lt;/emphasis&gt;. Que peut-on faire ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a de l'énergie. Que peut-on faire ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1447,7 +1424,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>On peut jouer, attendre, ou demander à un adulte. Que fait-on ?</t>
+          <t>On peut jouer, attendre, ou demander à un adulte. Que fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1576,7 +1553,6 @@
 narrateur|Que peut-on faire ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>L'eau du bac brille sous l'arbre. Chouchou a de l'énergie. Ce n'est pas une faute. Amir a joué. Il a su attendre. Il a demandé à un adulte. Tu as demandé, Amir ? Oui, papa. Bravo. Tu as fait du bon travail. Ils versent encore un peu d'eau.</t>
+          <t>Amir va vers papa. Papa, on fait quoi ? On fait flotter le bateau. On attend dans la file. Tu es venu me demander. On marche jusqu'au bac. Papa marche avec Chouchou. L'eau est froide. Chouchou pose les mains un moment. Elle souffle. L'énergie est encore là. Ce n'est pas une faute. On peut attendre. Chouchou reste dans la file. Amir pose la feuille sur l'eau. Elle tourne, tout lentement. On la laisse flotter ? Oui. Chouchou regarde la feuille. Elle attend. Puis elle pousse une toute petite vague. La feuille avance. Ils jouent. Amir attend son tour pour verser. Il verse un filet. La feuille fait un tour. Chacun son tour. Encore un tour. Encore un, tout doux. Une petite araignée d'eau part. La feuille la suit, tout lentement. Elle avance. Votre bateau a un sillage.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noa a de l'&lt;emphasis level="moderate"&gt;énergie&lt;/emphasis&gt;. Ce n'est pas une faute. Baptiste a joué. Il a su attendre. Il a demandé à un adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir va vers papa. Papa, on fait quoi ? On fait flotter le bateau. On attend dans la file. Tu es venu me demander. On marche jusqu'au bac. Papa marche avec Chouchou. L'eau est froide. Chouchou pose les mains un moment. Elle souffle. L'énergie est encore là. Ce n'est pas une faute. On peut attendre. Chouchou reste dans la file. Amir pose la feuille sur l'eau. Elle tourne, tout lentement. On la laisse flotter ? Oui. Chouchou regarde la feuille. Elle attend. Puis elle pousse une toute petite vague. La feuille avance. Ils jouent. Amir attend son tour pour verser. Il verse un filet. La feuille fait un tour. Chacun son tour. Encore un tour. Encore un, tout doux. Une petite araignée d'eau part. La feuille la suit, tout lentement. Elle avance. Votre bateau a un sillage.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1745,20 +1721,46 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|L'eau du bac brille sous l'arbre.
-narrateur|Chouchou a de l'énergie.
+          <t>narrateur|Amir va vers papa.
+enfant-m|Papa, on fait quoi ?
+papa|On fait flotter le bateau.
+papa|On attend dans la file.
+papa|Tu es venu me demander.
+papa|On marche jusqu'au bac.
+narrateur|Papa marche avec Chouchou.
+narrateur|L'eau est froide.
+narrateur|Chouchou pose les mains un moment.
+narrateur|Elle souffle.
+maman|L'énergie est encore là.
 maman|Ce n'est pas une faute.
-narrateur|Amir a joué.
-narrateur|Il a su attendre.
-narrateur|Il a demandé à un adulte.
-papa|Tu as demandé, Amir ?
-enfant-m|Oui, papa.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Ils versent encore un peu d'eau.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+enfant-m|On peut attendre.
+narrateur|Chouchou reste dans la file.
+narrateur|Amir pose la feuille sur l'eau.
+narrateur|Elle tourne, tout lentement.
+papa|On la laisse flotter ?
+enfant-m|Oui.
+narrateur|Chouchou regarde la feuille.
+narrateur|Elle attend.
+narrateur|Puis elle pousse une toute petite vague.
+narrateur|La feuille avance.
+narrateur|Ils jouent.
+narrateur|Amir attend son tour pour verser.
+narrateur|Il verse un filet.
+narrateur|La feuille fait un tour.
+maman|Chacun son tour.
+enfant-f|Encore un tour.
+papa|Encore un, tout doux.
+narrateur|Une petite araignée d'eau part.
+narrateur|La feuille la suit, tout lentement.
+enfant-m|Elle avance.
+maman|Votre bateau a un sillage.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,12 +1785,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On reprend le sac ? Oui, maman. Maman prend la main d'Amir. Chouchou range un cerceau. Vous vous dites au revoir ? Au revoir. Au revoir, Chouchou. Bravo. Belle file, aujourd'hui.</t>
+          <t>On reprend le sac ? Oui, maman. Maman prend la main d'Amir. Chouchou ramasse le morceau de craie. Vous vous dites au revoir ? Au revoir. Au revoir, Chouchou. La feuille reste un moment sur l'eau. Ton bateau a voyagé. Tout autour du bac. On la laisse là ? Elle sèche sur le bord.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Maman prend la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; de Baptiste. Noa range un cerceau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>On reprend le sac ? Oui, maman. Maman prend la main d'Amir. Chouchou ramasse le morceau de craie. Vous vous dites au revoir ? Au revoir. Au revoir, Chouchou. La feuille reste un moment sur l'eau. Ton bateau a voyagé. Tout autour du bac. On la laisse là ? Elle sèche sur le bord.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1926,15 +1928,17 @@
           <t>maman|On reprend le sac ?
 enfant-m|Oui, maman.
 narrateur|Maman prend la main d'Amir.
-narrateur|Chouchou range un cerceau.
+narrateur|Chouchou ramasse le morceau de craie.
 papa|Vous vous dites au revoir ?
-copain|Au revoir.
+enfant-f|Au revoir.
 enfant-m|Au revoir, Chouchou.
-papa|Bravo.
-papa|Belle file, aujourd'hui.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+narrateur|La feuille reste un moment sur l'eau.
+papa|Ton bateau a voyagé.
+enfant-m|Tout autour du bac.
+maman|On la laisse là ?
+enfant-m|Elle sèche sur le bord.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1959,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a fait la file du cerceau. On a attendu. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,14 +2103,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a fait la file du cerceau.
-enfant-m|On a attendu.
-papa|Bravo.
-maman|Tu as fait du bon travail.
+          <t>narrateur|La feuille jaune sèche sur le bord.
+narrateur|L'ombre de l'arbre a bougé.
+papa|Le bateau a fini son tour.
+enfant-m|Il a flotté.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2125,7 +2128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2198,6 +2201,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -1963,12 +1963,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté. L'histoire est finie.</t>
+          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté. L'histoire est finie.</t>
+          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2106,8 +2106,7 @@
           <t>narrateur|La feuille jaune sèche sur le bord.
 narrateur|L'ombre de l'arbre a bougé.
 papa|Le bateau a fini son tour.
-enfant-m|Il a flotté.
-narrateur|L'histoire est finie.</t>
+enfant-m|Il a flotté.</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2206,6 +2205,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cour d'école puis jardin</t>
+          <t>jardin de l'école, bac sous l'arbre</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Baptiste, Noa, maman</t>
+          <t>Amir, Chouchou, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
+++ b/stories/arbres/ATOM-DIF.ENE.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bateau-feuille</t>
+          <t>La file du cerceau</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin de l'école, bac sous l'arbre</t>
+          <t>cour d'école puis jardin, ombre d'arbre, cloche lointaine, cerceau rouge dans l'herbe, lacet, gourde, file</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir veut faire flotter une feuille jaune dans le bac. Chouchou arrive avec beaucoup d'énergie. L'eau éclabousse. Ils jouent, ils attendent, Amir demande à papa. La feuille tourne, tout lentement.</t>
+          <t>Le lacet glisse. Papa noue. Sur le nœud, un éclat de lacet brille. Cloche lointaine, ombre, cerceau rouge dans l'herbe. Amir veut la file, maintenant. Chouchou saute trop. Le cerceau part. Sourire parti. Il refuse de foncer. Merci vécu. Racine, elle veut passer. Il s'arrête, lit l'éclat. Un éclat de lacet tient sur le nœud.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une craie blanche a roulé sous le banc. Elle a un ventre cassé. Un morceau reste, tout sec. L'ombre du grand arbre fait des taches par terre. Une cloche lointaine fait ding, tout loin. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir ramasse une feuille jaune. Elle est sèche. Elle a des nervures. Elle craque un tout petit peu. Je veux un bateau. Dans le bac. Le bac est sous l'arbre. Amir souffle sur la feuille. Elle tremble dans sa main. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Elle a beaucoup d'énergie. Elle tourne. Elle s'arrête. Elle recommence. Elle saute tout le temps. C'est son énergie. Ce n'est pas une faute. Ils font une file pour le bac. Chouchou a envie d'aller vite. L'eau éclabousse un peu. Ma feuille. La feuille jaune tremble au bord. Amir regarde papa.</t>
+          <t>Le lacet glisse entre les doigts de papa. Le bout plastique fait clic, sec et petit. Ça a fait clic ! Ton lacet, Amir ? Oui, papa. Papa noue le nœud, un peu serré. Sur le nœud, un éclat de lacet brille. Il brille, papa. Tu le vois, sur le nœud ? Oui, un petit point. La cour sent l'herbe chaude, un peu. Ça sent l'herbe, maman. Tes chaussures tiennent, Amir ? Oui, maman. Une cloche lointaine fait ding, loin dans l'air. J'ai entendu le ding. La cloche, Amir ? Oui, loin. L'ombre de l'arbre est longue, sur la cour. Maman glisse une gourde dans le sac. L'eau est fraîche. Elle est froide, maman. Ils passent de la cour au jardin. L'herbe est haute, un peu sèche. Je veux le cerceau, maintenant ! Le cerceau dans l'herbe ? Oui, tout de suite. Jusqu'à l'arbre ? Oui, maman. Un cerceau rouge repose dans l'herbe. Le plastique est tiède, un peu rêche. Il est chaud, papa. Tu le tiens, Amir ? Oui, papa. En ce moment, Amir tient le cerceau. Ils font une file vers l'arbre. Moi d'abord, maintenant ! Les chaussures tapent le sol, depuis la cour. Chouchou arrive en sautant. J'arrive ! Chouchou ! Elle saute sur place, trop vite. Le cerceau ! Moi, le cerceau, maintenant ! Chouchou prend le cerceau rouge. Elle le fait tourner trop vite. Le cerceau part vers la gourde. Il part ! Oh. Le cerceau tombe dans l'herbe. Ça fait un bruit mou. Il est tombé ! L'éclat de lacet tremble, puis tient. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Chouchou, Amir ? Oui, papa. Tes mains sont chaudes, Amir ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une craie blanche a roulé sous le banc. Elle a un ventre cassé. Un morceau reste, tout sec. L'ombre du grand arbre fait des taches par terre. Une cloche lointaine fait ding, tout loin. Papa noue un lacet. Ton lacet est prêt, Amir ? Oui, papa. Maman glisse une gourde dans le sac. L'eau est fraîche. En ce moment, Amir ramasse une feuille jaune. Elle est sèche. Elle a des nervures. Elle craque un tout petit peu. Je veux un bateau. Dans le bac. Le bac est sous l'arbre. Amir souffle sur la feuille. Elle tremble dans sa main. Les chaussures tapent le sol de la cour. Chouchou arrive en sautant. Elle a beaucoup d'énergie. Elle tourne. Elle s'arrête. Elle recommence. Elle saute tout le temps. C'est son énergie. Ce n'est pas une faute. Ils font une file pour le bac. Chouchou a envie d'aller vite. L'eau éclabousse un peu. Ma feuille. La feuille jaune tremble au bord. Amir regarde papa.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le lacet glisse entre les doigts de papa. Le bout plastique fait clic, sec et petit. Ça a fait clic ! Ton lacet, Amir ? Oui, papa. Papa noue le nœud, un peu serré. Sur le nœud, un &lt;emphasis level="moderate"&gt;éclat de lacet&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur le nœud ? Oui, un petit point. La cour sent l'herbe chaude, un peu. Ça sent l'herbe, maman. Tes chaussures tiennent, Amir ? Oui, maman. Une cloche lointaine fait ding, loin dans l'air. J'ai entendu le ding. La cloche, Amir ? Oui, loin. L'ombre de l'arbre est longue, sur la cour. Maman glisse une gourde dans le sac. L'eau est fraîche. Elle est froide, maman. Ils passent de la cour au jardin. L'herbe est haute, un peu sèche. Je veux le cerceau, maintenant ! Le cerceau dans l'herbe ? Oui, tout de suite. Jusqu'à l'arbre ? Oui, maman. Un cerceau rouge repose dans l'herbe. Le plastique est tiède, un peu rêche. Il est chaud, papa. Tu le tiens, Amir ? Oui, papa. En ce moment, Amir tient le cerceau. Ils font une file vers l'arbre. Moi d'abord, maintenant ! Les chaussures tapent le sol, depuis la cour. Chouchou arrive en sautant. J'arrive ! Chouchou ! Elle saute sur place, trop vite. Le cerceau ! Moi, le cerceau, maintenant ! Chouchou prend le cerceau rouge. Elle le fait tourner trop vite. Le cerceau part vers la gourde. Il part ! Oh. Le cerceau tombe dans l'herbe. Ça fait un bruit mou. Il est tombé ! L'éclat de lacet tremble, puis tient. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Chouchou, Amir ? Oui, papa. Tes mains sont chaudes, Amir ? Un peu, maman.&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Maman laisse Baptiste dans la cour. Les chaussures tapent le sol. Noa arrive en sautant. Il a beaucoup d'&lt;emphasis&gt;énergie&lt;/emphasis&gt;. Il tourne. Il s'arrête. Il recommence. Baptiste le regarde. Maman est encore près du portail. Elle dit : beaucoup d'énergie, ce n'est pas une faute. On peut jouer. On peut attendre. On peut demander à un adulte. Baptiste hoche la tête. Ils font une file pour le cerceau. Noa a envie d'aller vite. Baptiste dit : on peut attendre. Noa souffle. Il reste dans la file. Ils jouent. Plus tard, au jardin de l'école, Noa a encore de l'énergie. Ce n'est pas une faute. Baptiste va vers la maîtresse. Il demande à un adulte. La maîtresse marche avec Noa jusqu'au bac. L'eau est froide. Puis ils versent l'eau ensemble. On peut jouer ou attendre. Maman revient. Baptiste dit : Noa a de l'énergie. Maman dit : ce n'est pas une faute. [pause]</t>
+          <t>Le lacet glisse entre les doigts de papa. Le bout plastique fait clic, sec et petit. Ça a fait clic ! Ton lacet, Amir ? Oui, papa. Papa noue le nœud, un peu serré. Sur le nœud, un &lt;emphasis&gt;éclat de lacet&lt;/emphasis&gt; brille. Il brille, papa. Tu le vois, sur le nœud ? Oui, un petit point. La cour sent l'herbe chaude, un peu. Ça sent l'herbe, maman. Tes chaussures tiennent, Amir ? Oui, maman. Une cloche lointaine fait ding, loin dans l'air. J'ai entendu le ding. La cloche, Amir ? Oui, loin. L'ombre de l'arbre est longue, sur la cour. Maman glisse une gourde dans le sac. L'eau est fraîche. Elle est froide, maman. Ils passent de la cour au jardin. L'herbe est haute, un peu sèche. Je veux le cerceau, maintenant ! Le cerceau dans l'herbe ? Oui, tout de suite. Jusqu'à l'arbre ? Oui, maman. Un cerceau rouge repose dans l'herbe. Le plastique est tiède, un peu rêche. Il est chaud, papa. Tu le tiens, Amir ? Oui, papa. En ce moment, Amir tient le cerceau. Ils font une file vers l'arbre. Moi d'abord, maintenant ! Les chaussures tapent le sol, depuis la cour. Chouchou arrive en sautant. J'arrive ! Chouchou ! Elle saute sur place, trop vite. Le cerceau ! Moi, le cerceau, maintenant ! Chouchou prend le cerceau rouge. Elle le fait tourner trop vite. Le cerceau part vers la gourde. Il part ! Oh. Le cerceau tombe dans l'herbe. Ça fait un bruit mou. Il est tombé ! L'éclat de lacet tremble, puis tient. Le sourire d'Amir disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Ses épaules tombent un peu. Papa s'accroupit à la même hauteur. Tu vois Chouchou, Amir ? Oui, papa. Tes mains sont chaudes, Amir ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>énergie</t>
+          <t>éclat de lacet</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1321,43 +1321,74 @@
       <c r="AU2" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_la_file_du_cerceau_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Une craie blanche a roulé sous le banc.
-narrateur|Elle a un ventre cassé.
-narrateur|Un morceau reste, tout sec.
-narrateur|L'ombre du grand arbre fait des taches par terre.
-narrateur|Une cloche lointaine fait ding, tout loin.
-narrateur|Papa noue un lacet.
-papa|Ton lacet est prêt, Amir ?
+          <t>narrateur|Le lacet glisse entre les doigts de papa.
+narrateur|Le bout plastique fait clic, sec et petit.
+enfant-m|Ça a fait clic !
+papa|Ton lacet, Amir ?
 enfant-m|Oui, papa.
+narrateur|Papa noue le nœud, un peu serré.
+narrateur|Sur le nœud, un éclat de lacet brille.
+enfant-m|Il brille, papa.
+papa|Tu le vois, sur le nœud ?
+enfant-m|Oui, un petit point.
+narrateur|La cour sent l'herbe chaude, un peu.
+enfant-m|Ça sent l'herbe, maman.
+maman|Tes chaussures tiennent, Amir ?
+enfant-m|Oui, maman.
+narrateur|Une cloche lointaine fait ding, loin dans l'air.
+enfant-m|J'ai entendu le ding.
+papa|La cloche, Amir ?
+enfant-m|Oui, loin.
+narrateur|L'ombre de l'arbre est longue, sur la cour.
 narrateur|Maman glisse une gourde dans le sac.
 maman|L'eau est fraîche.
-narrateur|En ce moment, Amir ramasse une feuille jaune.
-narrateur|Elle est sèche.
-narrateur|Elle a des nervures.
-narrateur|Elle craque un tout petit peu.
-enfant-m|Je veux un bateau.
-enfant-m|Dans le bac.
-papa|Le bac est sous l'arbre.
-narrateur|Amir souffle sur la feuille.
-narrateur|Elle tremble dans sa main.
-narrateur|Les chaussures tapent le sol de la cour.
+enfant-m|Elle est froide, maman.
+narrateur|Ils passent de la cour au jardin.
+narrateur|L'herbe est haute, un peu sèche.
+enfant-m|Je veux le cerceau, maintenant !
+papa|Le cerceau dans l'herbe ?
+enfant-m|Oui, tout de suite.
+maman|Jusqu'à l'arbre ?
+enfant-m|Oui, maman.
+narrateur|Un cerceau rouge repose dans l'herbe.
+narrateur|Le plastique est tiède, un peu rêche.
+enfant-m|Il est chaud, papa.
+papa|Tu le tiens, Amir ?
+enfant-m|Oui, papa.
+narrateur|En ce moment, Amir tient le cerceau.
+narrateur|Ils font une file vers l'arbre.
+enfant-m|Moi d'abord, maintenant !
+narrateur|Les chaussures tapent le sol, depuis la cour.
 narrateur|Chouchou arrive en sautant.
-narrateur|Elle a beaucoup d'énergie.
-narrateur|Elle tourne.
-narrateur|Elle s'arrête.
-narrateur|Elle recommence.
-enfant-m|Elle saute tout le temps.
-maman|C'est son énergie.
-maman|Ce n'est pas une faute.
-narrateur|Ils font une file pour le bac.
-narrateur|Chouchou a envie d'aller vite.
-narrateur|L'eau éclabousse un peu.
-enfant-m|Ma feuille.
-narrateur|La feuille jaune tremble au bord.
-narrateur|Amir regarde papa.</t>
+copine|J'arrive !
+enfant-m|Chouchou !
+narrateur|Elle saute sur place, trop vite.
+copine|Le cerceau !
+enfant-m|Moi, le cerceau, maintenant !
+narrateur|Chouchou prend le cerceau rouge.
+narrateur|Elle le fait tourner trop vite.
+narrateur|Le cerceau part vers la gourde.
+enfant-m|Il part !
+copine|Oh.
+narrateur|Le cerceau tombe dans l'herbe.
+narrateur|Ça fait un bruit mou.
+enfant-m|Il est tombé !
+narrateur|L'éclat de lacet tremble, puis tient.
+narrateur|Le sourire d'Amir disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa s'accroupit à la même hauteur.
+papa|Tu vois Chouchou, Amir ?
+enfant-m|Oui, papa.
+maman|Tes mains sont chaudes, Amir ?
+enfant-m|Un peu, maman.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1394,12 +1425,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a de l'énergie. Que peut-on faire ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Chouchou a de l'&lt;emphasis level="moderate"&gt;énergie&lt;/emphasis&gt;. Que peut-on faire ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Noa a de l'&lt;emphasis&gt;énergie&lt;/emphasis&gt;. Que peut-on faire ?</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Chouchou a de l'&lt;emphasis&gt;énergie&lt;/emphasis&gt;. Que peut-on faire ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1462,18 +1493,18 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1488,11 +1519,11 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="AH3" s="2" t="inlineStr">
         <is>
@@ -1503,23 +1534,23 @@
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1528,23 +1559,23 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
       </c>
       <c r="AU3" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=chouchou_a_de_l_energie_que_peut_on_faire; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1577,17 +1608,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir va vers papa. Papa, on fait quoi ? On fait flotter le bateau. On attend dans la file. Tu es venu me demander. On marche jusqu'au bac. Papa marche avec Chouchou. L'eau est froide. Chouchou pose les mains un moment. Elle souffle. L'énergie est encore là. Ce n'est pas une faute. On peut attendre. Chouchou reste dans la file. Amir pose la feuille sur l'eau. Elle tourne, tout lentement. On la laisse flotter ? Oui. Chouchou regarde la feuille. Elle attend. Puis elle pousse une toute petite vague. La feuille avance. Ils jouent. Amir attend son tour pour verser. Il verse un filet. La feuille fait un tour. Chacun son tour. Encore un tour. Encore un, tout doux. Une petite araignée d'eau part. La feuille la suit, tout lentement. Elle avance. Votre bateau a un sillage.</t>
+          <t>Amir veut le cerceau, tout de suite. Je le prends, maintenant ! Il avance trop vite vers Chouchou. Les mots se bousculent dans sa bouche. Attends. Chouchou saute, trop près de l'herbe. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il referme les mains. Personne ne parle. Il observe le cerceau, un instant. Il écoute la cloche, loin dans l'air. Tu veux le cerceau avec Chouchou ? Papa reste à la même hauteur. Papa, on fait quoi ? On reste dans la file ? Oui. On marche jusqu'à l'arbre ? Oui, maman. Viens, Chouchou. J'y vais. Ils restent dans la file, un moment. L'herbe froisse, sous les chaussures. L'herbe, papa. Tu poses les mains ? Oui. Amir pose les mains sur le plastique. Le cerceau est tiède. Chouchou pose les mains aussi. Il est chaud. Elle souffle. Merci, Amir. Papa a vu les deux, dans l'herbe. L'ombre de l'arbre a bougé, un peu. Elle est longue. Chouchou pose le cerceau, sans se presser. À toi. D'accord. Amir fait rouler le cerceau. Le cerceau passe dans l'herbe. Il roule ! Oui. Tu le vois, le rond rouge ? Oui, papa. Tes chaussures tiennent ? Oui, maman. Le ventre d'Amir se desserre. Les épaules se relèvent un peu. On reste près de l'arbre ? Oui. Tes mains sont chaudes ? Un peu, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Amir va vers papa. Papa, on fait quoi ? On fait flotter le bateau. On attend dans la file. Tu es venu me demander. On marche jusqu'au bac. Papa marche avec Chouchou. L'eau est froide. Chouchou pose les mains un moment. Elle souffle. L'énergie est encore là. Ce n'est pas une faute. On peut attendre. Chouchou reste dans la file. Amir pose la feuille sur l'eau. Elle tourne, tout lentement. On la laisse flotter ? Oui. Chouchou regarde la feuille. Elle attend. Puis elle pousse une toute petite vague. La feuille avance. Ils jouent. Amir attend son tour pour verser. Il verse un filet. La feuille fait un tour. Chacun son tour. Encore un tour. Encore un, tout doux. Une petite araignée d'eau part. La feuille la suit, tout lentement. Elle avance. Votre bateau a un sillage.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amir veut le &lt;emphasis level="moderate"&gt;cerceau&lt;/emphasis&gt;, tout de suite. Je le prends, maintenant ! Il avance trop vite vers Chouchou. Les mots se bousculent dans sa bouche. Attends. Chouchou saute, trop près de l'herbe. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il referme les mains. Personne ne parle. Il observe le cerceau, un instant. Il écoute la cloche, loin dans l'air. Tu veux le cerceau avec Chouchou ? Papa reste à la même hauteur. Papa, on fait quoi ? On reste dans la file ? Oui. On marche jusqu'à l'arbre ? Oui, maman. Viens, Chouchou. J'y vais. Ils restent dans la file, un moment. L'herbe froisse, sous les chaussures. L'herbe, papa. Tu poses les mains ? Oui. Amir pose les mains sur le plastique. Le cerceau est tiède. Chouchou pose les mains aussi. Il est chaud. Elle souffle. Merci, Amir. Papa a vu les deux, dans l'herbe. L'ombre de l'arbre a bougé, un peu. Elle est longue. Chouchou pose le cerceau, sans se presser. À toi. D'accord. Amir fait rouler le cerceau. Le cerceau passe dans l'herbe. Il roule ! Oui. Tu le vois, le rond rouge ? Oui, papa. Tes chaussures tiennent ? Oui, maman. Le ventre d'Amir se desserre. Les épaules se relèvent un peu. On reste près de l'arbre ? Oui. Tes mains sont chaudes ? Un peu, maman.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Noa a de l'&lt;emphasis&gt;énergie&lt;/emphasis&gt;. Ce n'est pas une faute. Baptiste a joué. Il a su attendre. Il a demandé à un adulte. [pause]</t>
+          <t>Amir veut le &lt;emphasis&gt;cerceau&lt;/emphasis&gt;, tout de suite. Je le prends, maintenant ! Il avance trop vite vers Chouchou. Les mots se bousculent dans sa bouche. Attends. Chouchou saute, trop près de l'herbe. Oh. Le sourire ne revient pas. Amir refuse de foncer. Il referme les mains. Personne ne parle. Il observe le cerceau, un instant. Il écoute la cloche, loin dans l'air. Tu veux le cerceau avec Chouchou ? Papa reste à la même hauteur. Papa, on fait quoi ? On reste dans la file ? Oui. On marche jusqu'à l'arbre ? Oui, maman. Viens, Chouchou. J'y vais. Ils restent dans la file, un moment. L'herbe froisse, sous les chaussures. L'herbe, papa. Tu poses les mains ? Oui. Amir pose les mains sur le plastique. Le cerceau est tiède. Chouchou pose les mains aussi. Il est chaud. Elle souffle. Merci, Amir. Papa a vu les deux, dans l'herbe. L'ombre de l'arbre a bougé, un peu. Elle est longue. Chouchou pose le cerceau, sans se presser. À toi. D'accord. Amir fait rouler le cerceau. Le cerceau passe dans l'herbe. Il roule ! Oui. Tu le vois, le rond rouge ? Oui, papa. Tes chaussures tiennent ? Oui, maman. Le ventre d'Amir se desserre. Les épaules se relèvent un peu. On reste près de l'arbre ? Oui. Tes mains sont chaudes ? Un peu, maman. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1634,7 +1665,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1642,10 +1673,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1668,30 +1699,30 @@
       </c>
       <c r="AH4" s="2" t="inlineStr">
         <is>
-          <t>énergie</t>
+          <t>cerceau</t>
         </is>
       </c>
       <c r="AI4" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1700,10 +1731,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1716,44 +1747,64 @@
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=retenue puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_refuse_reste_dans_la_file_avec_elle; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amir va vers papa.
+          <t>narrateur|Amir veut le cerceau, tout de suite.
+enfant-m|Je le prends, maintenant !
+narrateur|Il avance trop vite vers Chouchou.
+narrateur|Les mots se bousculent dans sa bouche.
+copine|Attends.
+narrateur|Chouchou saute, trop près de l'herbe.
+enfant-m|Oh.
+narrateur|Le sourire ne revient pas.
+narrateur|Amir refuse de foncer.
+narrateur|Il referme les mains.
+narrateur|Personne ne parle.
+narrateur|Il observe le cerceau, un instant.
+narrateur|Il écoute la cloche, loin dans l'air.
+papa|Tu veux le cerceau avec Chouchou ?
+narrateur|Papa reste à la même hauteur.
 enfant-m|Papa, on fait quoi ?
-papa|On fait flotter le bateau.
-papa|On attend dans la file.
-papa|Tu es venu me demander.
-papa|On marche jusqu'au bac.
-narrateur|Papa marche avec Chouchou.
-narrateur|L'eau est froide.
-narrateur|Chouchou pose les mains un moment.
+papa|On reste dans la file ?
+enfant-m|Oui.
+maman|On marche jusqu'à l'arbre ?
+enfant-m|Oui, maman.
+papa|Viens, Chouchou.
+copine|J'y vais.
+narrateur|Ils restent dans la file, un moment.
+narrateur|L'herbe froisse, sous les chaussures.
+enfant-m|L'herbe, papa.
+papa|Tu poses les mains ?
+enfant-m|Oui.
+narrateur|Amir pose les mains sur le plastique.
+narrateur|Le cerceau est tiède.
+narrateur|Chouchou pose les mains aussi.
+copine|Il est chaud.
 narrateur|Elle souffle.
-maman|L'énergie est encore là.
-maman|Ce n'est pas une faute.
-enfant-m|On peut attendre.
-narrateur|Chouchou reste dans la file.
-narrateur|Amir pose la feuille sur l'eau.
-narrateur|Elle tourne, tout lentement.
-papa|On la laisse flotter ?
+papa|Merci, Amir.
+narrateur|Papa a vu les deux, dans l'herbe.
+maman|L'ombre de l'arbre a bougé, un peu.
+enfant-m|Elle est longue.
+narrateur|Chouchou pose le cerceau, sans se presser.
+copine|À toi.
+enfant-m|D'accord.
+narrateur|Amir fait rouler le cerceau.
+narrateur|Le cerceau passe dans l'herbe.
+enfant-m|Il roule !
+copine|Oui.
+papa|Tu le vois, le rond rouge ?
+enfant-m|Oui, papa.
+maman|Tes chaussures tiennent ?
+enfant-m|Oui, maman.
+narrateur|Le ventre d'Amir se desserre.
+narrateur|Les épaules se relèvent un peu.
+papa|On reste près de l'arbre ?
 enfant-m|Oui.
-narrateur|Chouchou regarde la feuille.
-narrateur|Elle attend.
-narrateur|Puis elle pousse une toute petite vague.
-narrateur|La feuille avance.
-narrateur|Ils jouent.
-narrateur|Amir attend son tour pour verser.
-narrateur|Il verse un filet.
-narrateur|La feuille fait un tour.
-maman|Chacun son tour.
-enfant-f|Encore un tour.
-papa|Encore un, tout doux.
-narrateur|Une petite araignée d'eau part.
-narrateur|La feuille la suit, tout lentement.
-enfant-m|Elle avance.
-maman|Votre bateau a un sillage.</t>
+maman|Tes mains sont chaudes ?
+enfant-m|Un peu, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1785,17 +1836,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On reprend le sac ? Oui, maman. Maman prend la main d'Amir. Chouchou ramasse le morceau de craie. Vous vous dites au revoir ? Au revoir. Au revoir, Chouchou. La feuille reste un moment sur l'eau. Ton bateau a voyagé. Tout autour du bac. On la laisse là ? Elle sèche sur le bord.</t>
+          <t>Ils vont sous l'arbre, dans le jardin. Une file, maintenant ! L'ombre glisse sur l'herbe. Chouchou veut passer, trop vite. Elle saute vers le tronc. Moi d'abord ! Le cerceau penche vers une racine. Ça tombe ! Amir avance les mains, trop vite. Puis il s'arrête net. Amir refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe le cerceau, un instant. Il écoute la cloche, loin dans l'air. Sur le nœud, un éclat de lacet luit. Là, sur le nœud. Tu restes, Chouchou ? Chouchou ne dit rien. Elle souffle, sans parler. Oui. Elle reste derrière lui. Le cerceau, maman ? Le rouge, Amir. Amir pousse, sans se presser. Le cerceau contourne la racine. À moi. Chouchou pousse à son tour. Tu as soufflé, Chouchou ? Un peu. L'ombre est fraîche, Amir ? Un peu, maman. Vous roulez ensemble ? Oui, papa. Ils roulent le cerceau jusqu'au tronc. Le plastique tape le bois, sans bruit. Il est arrivé. Il est arrivé. Le cerceau a de l'herbe, Amir ? Sur le bord.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>On reprend le sac ? Oui, maman. Maman prend la main d'Amir. Chouchou ramasse le morceau de craie. Vous vous dites au revoir ? Au revoir. Au revoir, Chouchou. La feuille reste un moment sur l'eau. Ton bateau a voyagé. Tout autour du bac. On la laisse là ? Elle sèche sur le bord.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Ils vont sous l'arbre, dans le jardin. Une file, maintenant ! L'ombre glisse sur l'herbe. Chouchou veut passer, trop vite. Elle saute vers le tronc. Moi d'abord ! Le cerceau penche vers une racine. Ça tombe ! Amir avance les mains, trop vite. Puis il s'arrête net. Amir refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe le cerceau, un instant. Il écoute la cloche, loin dans l'air. Sur le nœud, un &lt;emphasis level="moderate"&gt;éclat de lacet&lt;/emphasis&gt; luit. Là, sur le nœud. Tu restes, Chouchou ? Chouchou ne dit rien. Elle souffle, sans parler. Oui. Elle reste derrière lui. Le cerceau, maman ? Le rouge, Amir. Amir pousse, sans se presser. Le cerceau contourne la racine. À moi. Chouchou pousse à son tour. Tu as soufflé, Chouchou ? Un peu. L'ombre est fraîche, Amir ? Un peu, maman. Vous roulez ensemble ? Oui, papa. Ils roulent le cerceau jusqu'au tronc. Le plastique tape le bois, sans bruit. Il est arrivé. Il est arrivé. Le cerceau a de l'herbe, Amir ? Sur le bord.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Maman prend la &lt;emphasis&gt;main&lt;/emphasis&gt; de Baptiste. Noa range un cerceau. [pause]</t>
+          <t>Ils vont sous l'arbre, dans le jardin. Une file, maintenant ! L'ombre glisse sur l'herbe. Chouchou veut passer, trop vite. Elle saute vers le tronc. Moi d'abord ! Le cerceau penche vers une racine. Ça tombe ! Amir avance les mains, trop vite. Puis il s'arrête net. Amir refuse de foncer, cette fois. Ses mains se ferment, puis s'ouvrent. Personne ne dit la suite. Il observe le cerceau, un instant. Il écoute la cloche, loin dans l'air. Sur le nœud, un &lt;emphasis&gt;éclat de lacet&lt;/emphasis&gt; luit. Là, sur le nœud. Tu restes, Chouchou ? Chouchou ne dit rien. Elle souffle, sans parler. Oui. Elle reste derrière lui. Le cerceau, maman ? Le rouge, Amir. Amir pousse, sans se presser. Le cerceau contourne la racine. À moi. Chouchou pousse à son tour. Tu as soufflé, Chouchou ? Un peu. L'ombre est fraîche, Amir ? Un peu, maman. Vous roulez ensemble ? Oui, papa. Ils roulent le cerceau jusqu'au tronc. Le plastique tape le bois, sans bruit. Il est arrivé. Il est arrivé. Le cerceau a de l'herbe, Amir ? Sur le bord. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1842,7 +1893,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1850,10 +1901,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1876,30 +1927,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>main</t>
+          <t>éclat de lacet</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1908,10 +1959,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1922,21 +1973,58 @@
       <c r="AU5" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_foncer_racine_elle_souffle; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>maman|On reprend le sac ?
-enfant-m|Oui, maman.
-narrateur|Maman prend la main d'Amir.
-narrateur|Chouchou ramasse le morceau de craie.
-papa|Vous vous dites au revoir ?
-enfant-f|Au revoir.
-enfant-m|Au revoir, Chouchou.
-narrateur|La feuille reste un moment sur l'eau.
-papa|Ton bateau a voyagé.
-enfant-m|Tout autour du bac.
-maman|On la laisse là ?
-enfant-m|Elle sèche sur le bord.</t>
+          <t>narrateur|Ils vont sous l'arbre, dans le jardin.
+enfant-m|Une file, maintenant !
+narrateur|L'ombre glisse sur l'herbe.
+narrateur|Chouchou veut passer, trop vite.
+narrateur|Elle saute vers le tronc.
+copine|Moi d'abord !
+narrateur|Le cerceau penche vers une racine.
+enfant-m|Ça tombe !
+narrateur|Amir avance les mains, trop vite.
+narrateur|Puis il s'arrête net.
+narrateur|Amir refuse de foncer, cette fois.
+narrateur|Ses mains se ferment, puis s'ouvrent.
+narrateur|Personne ne dit la suite.
+narrateur|Il observe le cerceau, un instant.
+narrateur|Il écoute la cloche, loin dans l'air.
+narrateur|Sur le nœud, un éclat de lacet luit.
+enfant-m|Là, sur le nœud.
+enfant-m|Tu restes, Chouchou ?
+narrateur|Chouchou ne dit rien.
+narrateur|Elle souffle, sans parler.
+copine|Oui.
+narrateur|Elle reste derrière lui.
+enfant-m|Le cerceau, maman ?
+maman|Le rouge, Amir.
+narrateur|Amir pousse, sans se presser.
+narrateur|Le cerceau contourne la racine.
+copine|À moi.
+narrateur|Chouchou pousse à son tour.
+papa|Tu as soufflé, Chouchou ?
+copine|Un peu.
+maman|L'ombre est fraîche, Amir ?
+enfant-m|Un peu, maman.
+papa|Vous roulez ensemble ?
+enfant-m|Oui, papa.
+narrateur|Ils roulent le cerceau jusqu'au tronc.
+narrateur|Le plastique tape le bois, sans bruit.
+enfant-m|Il est arrivé.
+copine|Il est arrivé.
+maman|Le cerceau a de l'herbe, Amir ?
+enfant-m|Sur le bord.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
         </is>
       </c>
     </row>
@@ -1963,17 +2051,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté.</t>
+          <t>Ils restent près de l'arbre. Maman essuie un peu d'herbe. On a eu le cerceau, papa. Tu l'as vu, toi ? Oui, jusqu'au tronc. On est bien, ici. Amir tapote le plastique du doigt. Il a une trace d'herbe. Tu la vois, la trace ? Oui, maman. Le cerceau est resté, Amir. Oui, avec Chouchou. Le cerceau est resté. Ça sent l'herbe, un peu tiède. Et le lacet, maman. Oui, dans l'air. Les chaussures restent dans l'herbe. Un éclat de lacet tient sur le nœud.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>La feuille jaune sèche sur le bord. L'ombre de l'arbre a bougé. Le bateau a fini son tour. Il a flotté.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils restent près de l'arbre. Maman essuie un peu d'herbe. On a eu le cerceau, papa. Tu l'as vu, toi ? Oui, jusqu'au tronc. On est bien, ici. Amir tapote le plastique du doigt. Il a une trace d'herbe. Tu la vois, la trace ? Oui, maman. Le cerceau est resté, Amir. Oui, avec Chouchou. Le cerceau est resté. Ça sent l'herbe, un peu tiède. Et le lacet, maman. Oui, dans l'air. Les chaussures restent dans l'herbe. Un &lt;emphasis level="moderate"&gt;éclat de lacet&lt;/emphasis&gt; tient sur le nœud.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;L'histoire est finie.&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils restent près de l'arbre. Maman essuie un peu d'herbe. On a eu le cerceau, papa. Tu l'as vu, toi ? Oui, jusqu'au tronc. On est bien, ici. Amir tapote le plastique du doigt. Il a une trace d'herbe. Tu la vois, la trace ? Oui, maman. Le cerceau est resté, Amir. Oui, avec Chouchou. Le cerceau est resté. Ça sent l'herbe, un peu tiède. Et le lacet, maman. Oui, dans l'air. Les chaussures restent dans l'herbe. Un &lt;emphasis&gt;éclat de lacet&lt;/emphasis&gt; tient sur le nœud.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2020,18 +2108,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2040,12 +2128,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2054,17 +2142,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de lacet</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>280</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2073,11 +2165,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2086,27 +2178,45 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse_et_fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_noeud; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|La feuille jaune sèche sur le bord.
-narrateur|L'ombre de l'arbre a bougé.
-papa|Le bateau a fini son tour.
-enfant-m|Il a flotté.</t>
+          <t>narrateur|Ils restent près de l'arbre.
+narrateur|Maman essuie un peu d'herbe.
+enfant-m|On a eu le cerceau, papa.
+papa|Tu l'as vu, toi ?
+enfant-m|Oui, jusqu'au tronc.
+maman|On est bien, ici.
+narrateur|Amir tapote le plastique du doigt.
+enfant-m|Il a une trace d'herbe.
+maman|Tu la vois, la trace ?
+enfant-m|Oui, maman.
+papa|Le cerceau est resté, Amir.
+enfant-m|Oui, avec Chouchou.
+copine|Le cerceau est resté.
+narrateur|Ça sent l'herbe, un peu tiède.
+enfant-m|Et le lacet, maman.
+maman|Oui, dans l'air.
+narrateur|Les chaussures restent dans l'herbe.
+narrateur|Un éclat de lacet tient sur le nœud.</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2212,6 +2322,13 @@
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
